--- a/Unity/Assets/Config/Excel/TitleConfig.xlsx
+++ b/Unity/Assets/Config/Excel/TitleConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="TitleProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="I3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,11 +60,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="80">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>AddProperty</t>
+  </si>
+  <si>
+    <t>AnimatorAsset</t>
+  </si>
+  <si>
+    <t>AnimatorNumber</t>
+  </si>
+  <si>
+    <t>ValidityTime</t>
+  </si>
+  <si>
+    <t>Des</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>MoveX</t>
+  </si>
+  <si>
+    <t>MoveY</t>
+  </si>
+  <si>
+    <t>GetDes</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -93,48 +144,6 @@
   </si>
   <si>
     <t>Y便宜</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>AddProperty</t>
-  </si>
-  <si>
-    <t>AnimatorAsset</t>
-  </si>
-  <si>
-    <t>AnimatorNumber</t>
-  </si>
-  <si>
-    <t>ValidityTime</t>
-  </si>
-  <si>
-    <t>Des</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>MoveX</t>
-  </si>
-  <si>
-    <t>MoveY</t>
-  </si>
-  <si>
-    <t>GetDes</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>double</t>
   </si>
   <si>
     <t>武林新丁</t>
@@ -303,7 +312,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +322,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -830,146 +845,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1320,713 +1338,719 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:V28"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.75" style="2" customWidth="1"/>
-    <col min="11" max="13" width="9" style="2"/>
-    <col min="14" max="14" width="18.75" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="12.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.75" style="2" customWidth="1"/>
+    <col min="10" max="12" width="9" style="2"/>
+    <col min="13" max="13" width="18.75" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1"/>
-    <row r="3" ht="20.1" customHeight="1" spans="3:14">
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="1" ht="20.1" customHeight="1" spans="1:13">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>7</v>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:14">
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
+    <row r="2" ht="20.1" customHeight="1" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:13">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:18">
+      <c r="B4" s="5">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="5">
+        <v>10001</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B5" s="5">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="5">
+        <v>10002</v>
+      </c>
+      <c r="G5" s="5">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B6" s="5">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="5">
+        <v>10008</v>
+      </c>
+      <c r="G6" s="5">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" s="1"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B7" s="5">
+        <v>10004</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="5">
+        <v>10004</v>
+      </c>
+      <c r="G7" s="5">
+        <v>10</v>
+      </c>
+      <c r="H7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="5">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B8" s="5">
+        <v>100041</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="5">
+        <v>10016</v>
+      </c>
+      <c r="G8" s="5">
+        <v>10</v>
+      </c>
+      <c r="H8" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="5">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B9" s="5">
+        <v>10005</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="5">
+        <v>10005</v>
+      </c>
+      <c r="G9" s="5">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B10" s="5">
+        <v>10006</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="5">
+        <v>10006</v>
+      </c>
+      <c r="G10" s="5">
         <v>11</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="H10" s="5">
+        <v>86400</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="5">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5">
+        <v>-25</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="S10" s="1"/>
+      <c r="U10" s="1"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:14">
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>23</v>
-      </c>
+    <row r="11" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B11" s="5">
+        <v>10007</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="5">
+        <v>10007</v>
+      </c>
+      <c r="G11" s="5">
+        <v>11</v>
+      </c>
+      <c r="H11" s="5">
+        <v>86400</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5">
+        <v>-25</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="U11" s="1"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:19">
-      <c r="C6" s="4">
+    <row r="12" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B12" s="5">
+        <v>10008</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="5">
         <v>10001</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="E12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="5">
+        <v>10003</v>
+      </c>
+      <c r="G12" s="5">
+        <v>11</v>
+      </c>
+      <c r="H12" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="5">
+        <v>2</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="S12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B13" s="5">
+        <v>10009</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="5">
         <v>10001</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="E13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="5">
+        <v>10009</v>
+      </c>
+      <c r="G13" s="5">
+        <v>11</v>
+      </c>
+      <c r="H13" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B14" s="5">
+        <v>10011</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="5">
         <v>10001</v>
       </c>
-      <c r="H6" s="4">
+      <c r="E14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="5">
+        <v>10011</v>
+      </c>
+      <c r="G14" s="5">
+        <v>40</v>
+      </c>
+      <c r="H14" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="5">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="S14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B15" s="5">
+        <v>10013</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10013</v>
+      </c>
+      <c r="G15" s="5">
+        <v>11</v>
+      </c>
+      <c r="H15" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" s="5">
+        <v>2</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="S15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B16" s="5">
+        <v>10014</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="5">
+        <v>10014</v>
+      </c>
+      <c r="G16" s="5">
+        <v>9</v>
+      </c>
+      <c r="H16" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" s="5">
+        <v>2</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="S16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="2:21">
+      <c r="B17" s="5">
+        <v>10015</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="5">
+        <v>10015</v>
+      </c>
+      <c r="G17" s="5">
         <v>10</v>
       </c>
-      <c r="I6" s="4">
+      <c r="H17" s="5">
         <v>-1</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="4">
+      <c r="I17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J17" s="5">
         <v>2</v>
       </c>
-      <c r="L6" s="4">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="S17" s="1"/>
+      <c r="U17" s="1"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C7" s="4">
-        <v>10002</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="4">
-        <v>10002</v>
-      </c>
-      <c r="H7" s="4">
-        <v>8</v>
-      </c>
-      <c r="I7" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="4">
-        <v>2</v>
-      </c>
-      <c r="L7" s="4">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T7" s="1"/>
-      <c r="V7" s="1"/>
+    <row r="18" ht="20.1" customHeight="1" spans="19:21">
+      <c r="S18" s="1"/>
+      <c r="U18" s="1"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C8" s="4">
-        <v>10003</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="4">
-        <v>10008</v>
-      </c>
-      <c r="H8" s="4">
-        <v>10</v>
-      </c>
-      <c r="I8" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="4">
-        <v>2</v>
-      </c>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="T8" s="1"/>
-      <c r="V8" s="1"/>
-    </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C9" s="4">
-        <v>10004</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="4">
-        <v>10004</v>
-      </c>
-      <c r="H9" s="4">
-        <v>10</v>
-      </c>
-      <c r="I9" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="4">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T9" s="1"/>
-      <c r="V9" s="1"/>
-    </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C10" s="4">
-        <v>100041</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="4">
-        <v>10016</v>
-      </c>
-      <c r="H10" s="4">
-        <v>10</v>
-      </c>
-      <c r="I10" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="4">
-        <v>2</v>
-      </c>
-      <c r="L10" s="4">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="T10" s="1"/>
-      <c r="V10" s="1"/>
-    </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C11" s="4">
-        <v>10005</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="4">
-        <v>10005</v>
-      </c>
-      <c r="H11" s="4">
-        <v>20</v>
-      </c>
-      <c r="I11" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="4">
-        <v>2</v>
-      </c>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T11" s="1"/>
-      <c r="V11" s="1"/>
-    </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C12" s="4">
-        <v>10006</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="4">
-        <v>10006</v>
-      </c>
-      <c r="H12" s="4">
-        <v>11</v>
-      </c>
-      <c r="I12" s="4">
-        <v>86400</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12" s="4">
-        <v>2</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-25</v>
-      </c>
-      <c r="M12" s="4">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="T12" s="1"/>
-      <c r="V12" s="1"/>
-    </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C13" s="4">
-        <v>10007</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="4">
-        <v>10007</v>
-      </c>
-      <c r="H13" s="4">
-        <v>11</v>
-      </c>
-      <c r="I13" s="4">
-        <v>86400</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="4">
-        <v>2</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-25</v>
-      </c>
-      <c r="M13" s="4">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="T13" s="1"/>
-      <c r="V13" s="1"/>
-    </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C14" s="4">
-        <v>10008</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="4">
-        <v>10003</v>
-      </c>
-      <c r="H14" s="4">
-        <v>11</v>
-      </c>
-      <c r="I14" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K14" s="4">
-        <v>2</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T14" s="1"/>
-      <c r="V14" s="1"/>
-    </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C15" s="4">
-        <v>10009</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="4">
-        <v>10009</v>
-      </c>
-      <c r="H15" s="4">
-        <v>11</v>
-      </c>
-      <c r="I15" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="K15" s="4">
-        <v>2</v>
-      </c>
-      <c r="L15" s="4">
-        <v>0</v>
-      </c>
-      <c r="M15" s="4">
-        <v>0</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="T15" s="1"/>
-      <c r="V15" s="1"/>
-    </row>
-    <row r="16" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C16" s="4">
-        <v>10011</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="4">
-        <v>10011</v>
-      </c>
-      <c r="H16" s="4">
-        <v>40</v>
-      </c>
-      <c r="I16" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K16" s="4">
-        <v>2</v>
-      </c>
-      <c r="L16" s="4">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="T16" s="1"/>
-      <c r="V16" s="1"/>
-    </row>
-    <row r="17" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C17" s="4">
-        <v>10013</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="4">
-        <v>10013</v>
-      </c>
-      <c r="H17" s="4">
-        <v>11</v>
-      </c>
-      <c r="I17" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="4">
-        <v>2</v>
-      </c>
-      <c r="L17" s="4">
-        <v>0</v>
-      </c>
-      <c r="M17" s="4">
-        <v>0</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T17" s="1"/>
-      <c r="V17" s="1"/>
-    </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C18" s="4">
-        <v>10014</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="4">
-        <v>10014</v>
-      </c>
-      <c r="H18" s="4">
-        <v>9</v>
-      </c>
-      <c r="I18" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" s="4">
-        <v>2</v>
-      </c>
-      <c r="L18" s="4">
-        <v>0</v>
-      </c>
-      <c r="M18" s="4">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="T18" s="1"/>
-      <c r="V18" s="1"/>
-    </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C19" s="4">
-        <v>10015</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="4">
-        <v>10001</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="4">
-        <v>10015</v>
-      </c>
-      <c r="H19" s="4">
-        <v>10</v>
-      </c>
-      <c r="I19" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="K19" s="4">
-        <v>2</v>
-      </c>
-      <c r="L19" s="4">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4">
-        <v>0</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="T19" s="1"/>
-      <c r="V19" s="1"/>
-    </row>
-    <row r="20" ht="20.1" customHeight="1" spans="20:22">
-      <c r="T20" s="1"/>
-      <c r="V20" s="1"/>
-    </row>
+    <row r="19" ht="20.1" customHeight="1"/>
+    <row r="20" ht="20.1" customHeight="1"/>
     <row r="21" ht="20.1" customHeight="1"/>
     <row r="22" ht="20.1" customHeight="1"/>
     <row r="23" ht="20.1" customHeight="1"/>
     <row r="24" ht="20.1" customHeight="1"/>
     <row r="25" ht="20.1" customHeight="1"/>
     <row r="26" ht="20.1" customHeight="1"/>
-    <row r="27" ht="20.1" customHeight="1"/>
-    <row r="28" ht="20.1" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
